--- a/30_output_share/_archive/20260830/05_지표GOLD매핑.xlsx
+++ b/30_output_share/_archive/20260830/05_지표GOLD매핑.xlsx
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-11 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-02 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-11</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-02</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 231,012/243,545 (94.9%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,452 (94.1%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 231,012/243,545 (94.9%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,452 (94.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 231,012/243,545 (94.9%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,452 (94.1%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 173,825/243,545 (71.4%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 182,977/255,452 (71.6%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.GA_CONV_MEMBERS` 비영 45,823/243,545 (18.8%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.GA_CONV_MEMBERS` 비영 47,987/255,452 (18.8%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,144행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,144행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,144행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,144행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr"/>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,144행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 196,572/243,545 (80.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 205,407/255,452 (80.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 173,825/243,545 (71.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 182,977/255,452 (71.6%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 21,455/243,545 (8.8%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 22,078/255,452 (8.6%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
@@ -2932,12 +2932,12 @@
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
@@ -2999,12 +2999,12 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
@@ -3012,14 +3012,14 @@
           <t>회원번호 기준, 회원상태가 활동인 회원의 총 개발 건 ( = 전체 후원금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L41" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -3066,12 +3066,12 @@
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
@@ -3524,14 +3524,14 @@
           <t>월말활동회원건 / 총 개발회원건 (연도초활동회원건 + 누계개발건)</t>
         </is>
       </c>
-      <c r="L49" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
@@ -3658,14 +3658,14 @@
           <t>활동 건 / (누계개발 건 + 연도초활동 건)</t>
         </is>
       </c>
-      <c r="L51" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L51" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -3775,12 +3775,12 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
@@ -3788,14 +3788,14 @@
           <t>전년도 연도말 활동회원 건수</t>
         </is>
       </c>
-      <c r="L53" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.YEAR_START_ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.YEAR_START_ACTIVE_CNT` 비영 35,527,740/40,054,883 (88.7%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -3972,12 +3972,12 @@
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
@@ -3985,14 +3985,14 @@
           <t>월 활동회원(회원상태가 활동, 미납1~미납5)의 전체후원사업금액 / 10,000</t>
         </is>
       </c>
-      <c r="L56" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L56" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -4039,23 +4039,23 @@
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr"/>
-      <c r="L57" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PREV_MONTH_END_ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PREV_MONTH_END_ACTIVE_CNT` 비영 37,695,311/40,054,883 (94.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
@@ -4568,14 +4568,14 @@
           <t>활동회원 건 / 활동회원 명</t>
         </is>
       </c>
-      <c r="L65" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L65" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
@@ -5713,12 +5713,12 @@
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="M86" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_REASON` 5,839행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_REASON` 5,854행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT.SEND_MEMBERS` 비영 38,470,780/38,470,780 (100.0%)</t>
+          <t>실측: `FACT_SERVICE_EVENT.SEND_MEMBERS` 비영 38,467,142/38,467,142 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
+          <t>CRM_SEND_MEMBER.SNDNG_RST_CD</t>
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
@@ -6179,14 +6179,14 @@
           <t>회원번호 개수 기준 (중복 포함)</t>
         </is>
       </c>
-      <c r="L90" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L90" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M90" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT.SUCCESS_MEMBERS` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_SERVICE_EVENT.SUCCESS_MEMBERS` 비영 24,263,968/38,467,142 (63.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -6233,12 +6233,12 @@
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_SEND_MEMBER.SNDNG_RST_CD</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
@@ -6246,14 +6246,14 @@
           <t>회원번호 개수 기준 (중복 포함)</t>
         </is>
       </c>
-      <c r="L91" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L91" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT.FAIL_MEMBERS` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_SERVICE_EVENT.FAIL_MEMBERS` 비영 1,986,871/38,467,142 (5.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
         </is>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
@@ -6560,10 +6560,14 @@
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>GA4_EVENT.EVENT_DT</t>
-        </is>
-      </c>
-      <c r="J96" s="4" t="inlineStr"/>
+          <t>BIGQUERY_EVENT.EVENT_DT</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K96" s="4" t="inlineStr"/>
       <c r="L96" s="5" t="inlineStr">
         <is>
@@ -6619,10 +6623,14 @@
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>GA4_EVENT.EVENT_DT</t>
-        </is>
-      </c>
-      <c r="J97" s="4" t="inlineStr"/>
+          <t>BIGQUERY_EVENT.EVENT_DT</t>
+        </is>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K97" s="4" t="inlineStr"/>
       <c r="L97" s="5" t="inlineStr">
         <is>
@@ -6678,10 +6686,14 @@
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>GA4_EVENT.EVENT_DT</t>
-        </is>
-      </c>
-      <c r="J98" s="4" t="inlineStr"/>
+          <t>BIGQUERY_EVENT.EVENT_DT</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K98" s="4" t="inlineStr"/>
       <c r="L98" s="5" t="inlineStr">
         <is>
@@ -6737,10 +6749,14 @@
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>GA4_EVENT.EVENT_DT</t>
-        </is>
-      </c>
-      <c r="J99" s="4" t="inlineStr"/>
+          <t>BIGQUERY_EVENT.EVENT_DT</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K99" s="4" t="inlineStr"/>
       <c r="L99" s="5" t="inlineStr">
         <is>
@@ -6796,10 +6812,14 @@
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>GA4_EVENT.EVENT_DT</t>
-        </is>
-      </c>
-      <c r="J100" s="4" t="inlineStr"/>
+          <t>BIGQUERY_EVENT.EVENT_DT</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K100" s="4" t="inlineStr"/>
       <c r="L100" s="5" t="inlineStr">
         <is>
@@ -6855,10 +6875,14 @@
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>GA4_EVENT.GA_SESSION_ID</t>
-        </is>
-      </c>
-      <c r="J101" s="4" t="inlineStr"/>
+          <t>BIGQUERY_EVENT.GA_SESSION_ID</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K101" s="4" t="inlineStr"/>
       <c r="L101" s="5" t="inlineStr">
         <is>
@@ -6867,7 +6891,7 @@
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_GA_BEHAVIOR.SESSION_CNT` 비영 68,836/68,836 (100.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_GA_BEHAVIOR.SESSION_CNT` 비영 4,376,338/4,376,339 (100.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -6969,10 +6993,14 @@
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>GA4_EVENT_DIM.EVENT_CATEGORY</t>
-        </is>
-      </c>
-      <c r="J103" s="4" t="inlineStr"/>
+          <t>BIGQUERY_EVENT_DIM.EVENT_CATEGORY</t>
+        </is>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
           <t>member_id가 (not set)이 아닌 데이터</t>
@@ -6985,7 +7013,7 @@
       </c>
       <c r="M103" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_GA_EVENT` 4,017행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_GA_EVENT` 78,661행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7032,10 +7060,14 @@
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>GA4_EVENT_DIM.EVENT_CATEGORY</t>
-        </is>
-      </c>
-      <c r="J104" s="4" t="inlineStr"/>
+          <t>BIGQUERY_EVENT_DIM.EVENT_CATEGORY</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
           <t>후원b1, 후원b2, 1단_대문, 퀵버튼 등</t>
@@ -7048,7 +7080,7 @@
       </c>
       <c r="M104" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_GA_EVENT` 4,017행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_GA_EVENT` 78,661행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7095,10 +7127,14 @@
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>GA4_EVENT_DIM.EVENT_CATEGORY</t>
-        </is>
-      </c>
-      <c r="J105" s="4" t="inlineStr"/>
+          <t>BIGQUERY_EVENT_DIM.EVENT_CATEGORY</t>
+        </is>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
           <t>member_id가 (not set)이 아닌 데이터</t>
@@ -7111,7 +7147,7 @@
       </c>
       <c r="M105" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_GA_EVENT` 4,017행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_GA_EVENT` 78,661행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7199,7 @@
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="K106" s="4" t="inlineStr">
@@ -7178,7 +7214,7 @@
       </c>
       <c r="M106" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,144행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7225,10 +7261,14 @@
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>GA4_TRAFFIC_SOURCE.UTM_SOURCE</t>
-        </is>
-      </c>
-      <c r="J107" s="4" t="inlineStr"/>
+          <t>BIGQUERY_TRAFFIC_SOURCE.UTM_SOURCE</t>
+        </is>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
           <t>기부금영수증 인쇄 / 로그인하기 / 전체메뉴보기 등</t>
@@ -7241,7 +7281,7 @@
       </c>
       <c r="M107" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_GA_SOURCE` 147행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_GA_SOURCE` 689행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7288,10 +7328,14 @@
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>GA4_TRAFFIC_SOURCE.UTM_SOURCE</t>
-        </is>
-      </c>
-      <c r="J108" s="4" t="inlineStr"/>
+          <t>BIGQUERY_TRAFFIC_SOURCE.UTM_SOURCE</t>
+        </is>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K108" s="4" t="inlineStr"/>
       <c r="L108" s="5" t="inlineStr">
         <is>
@@ -7300,7 +7344,7 @@
       </c>
       <c r="M108" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_GA_SOURCE` 147행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_GA_SOURCE` 689행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7461,10 +7505,14 @@
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>GA4_EVENT.PERCENT_SCROLLED</t>
-        </is>
-      </c>
-      <c r="J111" s="4" t="inlineStr"/>
+          <t>BIGQUERY_EVENT.PERCENT_SCROLLED</t>
+        </is>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K111" s="4" t="inlineStr"/>
       <c r="L111" s="5" t="inlineStr">
         <is>
@@ -7473,7 +7521,7 @@
       </c>
       <c r="M111" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_GA_BEHAVIOR.SCROLL_DEPTH` 비영 14,042/68,836 (20.4%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_GA_BEHAVIOR.SCROLL_DEPTH` 비영 904,700/4,376,339 (20.7%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -7575,10 +7623,14 @@
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>GA4_TRAFFIC_SOURCE.UTM_SOURCE</t>
-        </is>
-      </c>
-      <c r="J113" s="4" t="inlineStr"/>
+          <t>BIGQUERY_TRAFFIC_SOURCE.UTM_SOURCE</t>
+        </is>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K113" s="4" t="inlineStr"/>
       <c r="L113" s="5" t="inlineStr">
         <is>
@@ -7587,7 +7639,7 @@
       </c>
       <c r="M113" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_GA_SOURCE` 147행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_GA_SOURCE` 689행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8136,7 @@
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr"/>
@@ -8095,7 +8147,7 @@
       </c>
       <c r="M121" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,144행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8199,7 @@
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="K122" s="4" t="inlineStr"/>
@@ -8158,7 +8210,7 @@
       </c>
       <c r="M122" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,144행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8262,7 @@
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr"/>
@@ -8221,7 +8273,7 @@
       </c>
       <c r="M123" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,144행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8325,7 @@
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="K124" s="4" t="inlineStr"/>
@@ -8284,7 +8336,7 @@
       </c>
       <c r="M124" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,144행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9914,7 @@
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr"/>
@@ -9873,7 +9925,7 @@
       </c>
       <c r="M151" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,144행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9925,7 +9977,7 @@
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K152" s="4" t="inlineStr"/>
@@ -9988,7 +10040,7 @@
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K153" s="4" t="inlineStr"/>
@@ -10046,12 +10098,12 @@
       </c>
       <c r="I154" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K154" s="4" t="inlineStr"/>
@@ -10109,12 +10161,12 @@
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K155" s="4" t="inlineStr"/>
@@ -10408,23 +10460,23 @@
       </c>
       <c r="I160" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K160" s="4" t="inlineStr"/>
-      <c r="L160" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L160" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M160" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_MEMBERS` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_MEMBERS` 비영 38,423,125/40,054,883 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -10471,23 +10523,23 @@
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K161" s="4" t="inlineStr"/>
-      <c r="L161" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L161" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M161" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -10597,12 +10649,12 @@
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K163" s="4" t="inlineStr"/>
@@ -10802,7 +10854,7 @@
       </c>
       <c r="M166" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_REASON` 5,839행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_REASON` 5,854행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11091,7 @@
       </c>
       <c r="J170" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K170" s="4" t="inlineStr">
@@ -11530,12 +11582,12 @@
       </c>
       <c r="I178" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J178" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K178" s="4" t="inlineStr">
@@ -11543,14 +11595,14 @@
           <t>캠페인별 활동건 / (캠페인별 개발누계건 + 캠페인별 연도초활동건)</t>
         </is>
       </c>
-      <c r="L178" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L178" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M178" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -11597,12 +11649,12 @@
       </c>
       <c r="I179" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J179" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K179" s="4" t="inlineStr">
@@ -11610,14 +11662,14 @@
           <t>조회시점 기준 캠페인 활동건 / (캠페인 개발누계건 + 캠페인 연도초활동건)</t>
         </is>
       </c>
-      <c r="L179" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L179" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M179" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -11664,12 +11716,12 @@
       </c>
       <c r="I180" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J180" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K180" s="4" t="inlineStr">
@@ -11677,14 +11729,14 @@
           <t>캠페인별 납입방식 활동건 / (캠페인별 납입방식 개발누계건 + 캠페인별 납입방식 연도초활동건)</t>
         </is>
       </c>
-      <c r="L180" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L180" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M180" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -11736,7 +11788,7 @@
       </c>
       <c r="J181" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K181" s="4" t="inlineStr">
@@ -11803,7 +11855,7 @@
       </c>
       <c r="J182" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K182" s="4" t="inlineStr">
@@ -11870,7 +11922,7 @@
       </c>
       <c r="J183" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K183" s="4" t="inlineStr">
@@ -11937,7 +11989,7 @@
       </c>
       <c r="J184" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K184" s="4" t="inlineStr">
@@ -12004,7 +12056,7 @@
       </c>
       <c r="J185" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K185" s="4" t="inlineStr">
@@ -12066,12 +12118,12 @@
       </c>
       <c r="I186" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J186" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K186" s="4" t="inlineStr">
@@ -12133,12 +12185,12 @@
       </c>
       <c r="I187" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J187" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K187" s="4" t="inlineStr">
@@ -12535,12 +12587,12 @@
       </c>
       <c r="I193" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J193" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K193" s="4" t="inlineStr">
@@ -12602,12 +12654,12 @@
       </c>
       <c r="I194" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J194" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K194" s="4" t="inlineStr">
@@ -12669,12 +12721,12 @@
       </c>
       <c r="I195" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J195" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K195" s="4" t="inlineStr">
@@ -12756,7 +12808,7 @@
       </c>
       <c r="M196" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT.SEND_MEMBERS` 비영 38,470,780/38,470,780 (100.0%)</t>
+          <t>실측: `FACT_SERVICE_EVENT.SEND_MEMBERS` 비영 38,467,142/38,467,142 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -12803,12 +12855,12 @@
       </c>
       <c r="I197" s="4" t="inlineStr">
         <is>
-          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
+          <t>CRM_SEND_MEMBER.SNDNG_RST_CD</t>
         </is>
       </c>
       <c r="J197" s="4" t="inlineStr">
         <is>
-          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="K197" s="4" t="inlineStr">
@@ -12816,14 +12868,14 @@
           <t>발송성공수(명) / 발송수(명) × 100</t>
         </is>
       </c>
-      <c r="L197" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L197" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M197" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT.SUCCESS_MEMBERS` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_SERVICE_EVENT.SUCCESS_MEMBERS` 비영 24,263,968/38,467,142 (63.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12934,7 +12986,7 @@
       </c>
       <c r="J199" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K199" s="4" t="inlineStr">
@@ -13586,12 +13638,12 @@
       </c>
       <c r="I210" s="4" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
         </is>
       </c>
       <c r="J210" s="4" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="K210" s="4" t="inlineStr">
@@ -14177,7 +14229,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-11</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-02</t>
         </is>
       </c>
     </row>
@@ -15661,20 +15713,16 @@
           <t>문자</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>공13</t>
-        </is>
-      </c>
+      <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>DIM_AD_CREATIVE.PLATFORM_TYPE</t>
+          <t>(미매칭 — GOLD 물리·SV 대응 미확인)</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>필드인벤토리·별칭등록부</t>
+          <t>(미매칭)</t>
         </is>
       </c>
     </row>
@@ -15965,13 +16013,13 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>DIM_AD_CREATIVE.DURATION_SEC</t>
+          <t>DIM_AD_CREATIVE</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>지표사전</t>
         </is>
       </c>
     </row>
@@ -16259,20 +16307,16 @@
           <t>문자</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>(215밖)</t>
-        </is>
-      </c>
+      <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>DIM_AD_CREATIVE.TARGET_GROUP</t>
+          <t>(미매칭 — GOLD 물리·SV 대응 미확인)</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>필드인벤토리~</t>
+          <t>(미매칭)</t>
         </is>
       </c>
     </row>
@@ -17315,7 +17359,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-11</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-02</t>
         </is>
       </c>
     </row>
